--- a/sources/lei_step8.xlsx
+++ b/sources/lei_step8.xlsx
@@ -421,11 +421,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col hidden="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
     <col hidden="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col hidden="1" min="9" max="9"/>
@@ -3593,22 +3593,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>f,N+1 [u_d]</t>
+          <t>f,N+1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>f,N+1 [u_d]</t>
+          <t>f,N+1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Razor Rush [SNA]</t>
+          <t>Razor Rush</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Razor Rush [SNA]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3695,22 +3700,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2 [u_d]</t>
+          <t>f,N+1&lt;2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2 [u_d]</t>
+          <t>f,N+1&lt;2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Razor Rush [DGN]</t>
+          <t>Razor Rush</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Razor Rush [DGN]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>(~U)DGN; (~D)DGN</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3797,22 +3807,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2&lt;1 [u_d]</t>
+          <t>f,N+1&lt;2&lt;1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2&lt;1 [u_d]</t>
+          <t>f,N+1&lt;2&lt;1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Razor Rush [PAN]</t>
+          <t>Razor Rush</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Razor Rush [PAN]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>(~U)PAN; (~D)PAN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3899,22 +3914,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2&lt;1&lt;2 [u_d]</t>
+          <t>f,N+1&lt;2&lt;1&lt;2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2&lt;1&lt;2 [u_d]</t>
+          <t>f,N+1&lt;2&lt;1&lt;2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Razor Rush [TGR]</t>
+          <t>Razor Rush</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Razor Rush [TGR]</t>
+          <t>Razor Rush</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>(~U)TGR; (~D)TGR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4006,7 +4026,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2&lt;1&lt;2 [u_d],3</t>
+          <t>f,N+1&lt;2&lt;1&lt;2,3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4016,7 +4036,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Razor Rush [TGR] – Low Kick</t>
+          <t>Razor Rush – Low Kick</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4098,22 +4118,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>– &lt;4 [u_d]</t>
+          <t>– &lt;4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>f,N+1&lt;2&lt;1&lt;2 [u_d]&lt;4 [u_d]</t>
+          <t>f,N+1&lt;2&lt;1&lt;2&lt;4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>– Crane Kick [CRA]</t>
+          <t>– Crane Kick</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Razor Rush [TGR] – Crane Kick [CRA]</t>
+          <t>Razor Rush – Crane Kick</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4506,22 +4531,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>b+1 [~f]</t>
+          <t>b+1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>b+1 [~f]</t>
+          <t>b+1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Drunken Tiger Lash - [DRU]</t>
+          <t>Drunken Tiger Lash</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Drunken Tiger Lash - [DRU]</t>
+          <t>Drunken Tiger Lash</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4603,22 +4633,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SS+1 [~f] [~d_~u]</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SS+1 [~f] [~d_~u]</t>
+          <t>SS+1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Snake Strike [TGR] [DGN]</t>
+          <t>Snake Strike</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Snake Strike [TGR] [DGN]</t>
+          <t>Snake Strike</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>(~F)TGR; (~D)DGN; (~U)DGN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4700,22 +4735,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>f+1+2 [~f] [~d_~u]</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>f+1+2 [~f] [~d_~u]</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Twin Snake Strikes [CRA] [PAN]</t>
+          <t>Twin Snake Strikes</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Twin Snake Strikes [CRA] [PAN]</t>
+          <t>Twin Snake Strikes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>(~F)CRA; (~D)PAN; (~U)PAN</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5110,22 +5150,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>– &lt;4 [u_d]</t>
+          <t>– &lt;4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>f,N+2&lt;1&lt;2&lt;4 [u_d]</t>
+          <t>f,N+2&lt;1&lt;2&lt;4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>– Crane Kick [CRA]</t>
+          <t>– Crane Kick</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Breaking Rush – Crane Kick [CRA]</t>
+          <t>Breaking Rush – Crane Kick</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5172,22 +5217,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SS+2,2 [~f]</t>
+          <t>SS+2,2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SS+2,2 [~f]</t>
+          <t>SS+2,2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Drunken Rapid Fists [DRU]</t>
+          <t>Drunken Rapid Fists</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Drunken Rapid Fists [DRU]</t>
+          <t>Drunken Rapid Fists</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5376,27 +5426,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3~4 [d]</t>
+          <t>3~4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3~4 [d]</t>
+          <t>3~4</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND]</t>
+          <t>Tornado Kick</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND]</t>
+          <t>Tornado Kick</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5483,7 +5533,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>3~4 [d],2</t>
+          <t>3~4,2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5493,7 +5543,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND] – Tornado Upper</t>
+          <t>Tornado Kick – Tornado Upper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5565,27 +5615,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3~4,U [d]</t>
+          <t>3~4,U</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>3~4,U [d]</t>
+          <t>3~4,U</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Triple Tornado [KND]</t>
+          <t>Triple Tornado</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Triple Tornado [KND]</t>
+          <t>Triple Tornado</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5632,27 +5682,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>f+3~4 [d]</t>
+          <t>f+3~4</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>f+3~4 [d]</t>
+          <t>f+3~4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND]</t>
+          <t>Axis Shift Tornado Kick</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND]</t>
+          <t>Axis Shift Tornado Kick</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5739,7 +5789,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>f+3~4 [d],2</t>
+          <t>f+3~4,2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5749,7 +5799,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND] – Tornado Upper</t>
+          <t>Axis Shift Tornado Kick – Tornado Upper</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5821,27 +5871,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>f+3~4,U [d]</t>
+          <t>f+3~4,U</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>f+3~4,U [d]</t>
+          <t>f+3~4,U</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND]</t>
+          <t>Axis Shift Tornado Kick</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Axis Shift Tornado Kick [KND]</t>
+          <t>Axis Shift Tornado Kick</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -7186,22 +7236,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>–– &lt;4 [u_d]</t>
+          <t>–– &lt;4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>f+4,2,1&lt;2&lt;4 [u_d]</t>
+          <t>f+4,2,1&lt;2&lt;4</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>–– Crane Kick [CRA]</t>
+          <t>–– Crane Kick</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Beating Kick – Rush – Crane Kick [CRA]</t>
+          <t>Beating Kick – Rush – Crane Kick</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7283,22 +7338,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>db+4 [u_d]</t>
+          <t>db+4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>db+4 [u_d]</t>
+          <t>db+4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA]</t>
+          <t>Rave Sweep</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA]</t>
+          <t>Rave Sweep</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -7390,7 +7450,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>db+4 [u_d],4</t>
+          <t>db+4,4</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7400,7 +7460,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA] – Rave Spin</t>
+          <t>Rave Sweep – Rave Spin</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8339,22 +8399,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>– 1 [~F]</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>f+3+4,1 [~F]</t>
+          <t>f+3+4,1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>– Drunken Tiger Lash [DRU]</t>
+          <t>– Drunken Tiger Lash</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Drunken Master Parry – Drunken Tiger Lash [DRU]</t>
+          <t>Drunken Master Parry – Drunken Tiger Lash</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8436,22 +8501,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>– 2,2 [~F]</t>
+          <t>– 2,2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>f+3+4,2,2 [~F]</t>
+          <t>f+3+4,2,2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>– Drunken Rapid Fists [DRU]</t>
+          <t>– Drunken Rapid Fists</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Drunken Master Parry – Drunken Rapid Fists [DRU]</t>
+          <t>Drunken Master Parry – Drunken Rapid Fists</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>(~F)DRU</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -10142,27 +10212,32 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>FC+4 [u_d]</t>
+          <t>FC+4</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FC+4 [u_d]</t>
+          <t>FC+4</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>d+4 [u_d]</t>
+          <t>d+4</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA]</t>
+          <t>Rave Sweep</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA]</t>
+          <t>Rave Sweep</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10254,7 +10329,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FC+4 [u_d],4</t>
+          <t>FC+4,4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10264,7 +10339,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rave Sweep [SNA] – Rave Spin</t>
+          <t>Rave Sweep – Rave Spin</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11603,22 +11678,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>– 1 [u_d]</t>
+          <t>– 1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3,1 [u_d]</t>
+          <t>3,1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>– Razor Rush [SNA]</t>
+          <t>– Razor Rush</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [SNA]</t>
+          <t>Tiger Kick – Razor Rush</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>(~U)SNA; (~D)SNA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -11685,22 +11765,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>– 1&lt;2 [u_d]</t>
+          <t>– 1&lt;2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3,1&lt;2 [u_d]</t>
+          <t>3,1&lt;2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>– Razor Rush [DGN]</t>
+          <t>– Razor Rush</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [DGN]</t>
+          <t>Tiger Kick – Razor Rush</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>(~U)DGN; (~D)DGN</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -11767,22 +11852,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>– 1&lt;2&lt;1 [u_d]</t>
+          <t>– 1&lt;2&lt;1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>3,1&lt;2&lt;1 [u_d]</t>
+          <t>3,1&lt;2&lt;1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>– Razor Rush [PAN]</t>
+          <t>– Razor Rush</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [PAN]</t>
+          <t>Tiger Kick – Razor Rush</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>(~U)PAN; (~D)PAN</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -11849,22 +11939,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>– 1&lt;2&lt;1&lt;2 [u_d]</t>
+          <t>– 1&lt;2&lt;1&lt;2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>3,1&lt;2&lt;1&lt;2 [u_d]</t>
+          <t>3,1&lt;2&lt;1&lt;2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>– Razor Rush [TGR]</t>
+          <t>– Razor Rush</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [TGR]</t>
+          <t>Tiger Kick – Razor Rush</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>(~U)TGR; (~D)TGR</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11951,7 +12046,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>3,1&lt;2&lt;1&lt;2 [u_d],3</t>
+          <t>3,1&lt;2&lt;1&lt;2,3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -11961,7 +12056,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [TGR] – Low Kick</t>
+          <t>Tiger Kick – Razor Rush – Low Kick</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -12043,22 +12138,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>–– &lt;4 [u_d]</t>
+          <t>–– &lt;4</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3,1&lt;2&lt;1&lt;2 [u_d]&lt;4 [u_d]</t>
+          <t>3,1&lt;2&lt;1&lt;2&lt;4</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>–– Crane Kick [CRA]</t>
+          <t>–– Crane Kick</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tiger Kick – Razor Rush [TGR] – Crane Kick [CRA]</t>
+          <t>Tiger Kick – Razor Rush – Crane Kick</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -13185,22 +13285,27 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3 [~B]</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3 [~B]</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Panther Tail [Art of Phoenix]</t>
+          <t>Panther Tail</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Panther Tail [Art of Phoenix]</t>
+          <t>Panther Tail</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>(~B)AOP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -13578,22 +13683,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>–– &lt;4 [u_d]</t>
+          <t>–– &lt;4</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4,2,1&lt;2&lt;4 [u_d]</t>
+          <t>4,2,1&lt;2&lt;4</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>–– Crane Kick [CRA]</t>
+          <t>–– Crane Kick</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Beating Kick – Rush – Crane Kick [CRA]</t>
+          <t>Beating Kick – Rush – Crane Kick</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>(~U)CRA; (~D)CRA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -13949,22 +14059,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1+2 [~F]</t>
+          <t>1+2</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1+2 [~F]</t>
+          <t>1+2</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Dragon Spark - [TGR]</t>
+          <t>Dragon Spark</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dragon Spark - [TGR]</t>
+          <t>Dragon Spark</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>(~F)TGR</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -14051,22 +14166,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Dragon Roar - [TGR]</t>
+          <t>Dragon Roar</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Dragon Roar - [TGR]</t>
+          <t>Dragon Roar</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>(~F)TGR</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -14830,22 +14950,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1~1~1~1~1~1 [~F]</t>
+          <t>1~1~1~1~1~1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1~1~1~1~1~1 [~F]</t>
+          <t>1~1~1~1~1~1</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Rushing Snake [SNA]</t>
+          <t>Rushing Snake</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Rushing Snake [SNA]</t>
+          <t>Rushing Snake</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>(~F)SNA</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -14932,22 +15057,27 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2 [~F]</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Single Snake Bite [DGN]</t>
+          <t>Single Snake Bite</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Single Snake Bite [DGN]</t>
+          <t>Single Snake Bite</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>(~F)DGN</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -15034,22 +15164,27 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2,2 [~F]</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2,2 [~F]</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN]</t>
+          <t>Double Snake Bite</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN]</t>
+          <t>Double Snake Bite</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>(~F)DGN</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -15136,7 +15271,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2,2 [~F],4</t>
+          <t>2,2,4</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -15146,7 +15281,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN] – Ankle Kick</t>
+          <t>Double Snake Bite – Ankle Kick</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -15223,7 +15358,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2,2 [~F],4,3</t>
+          <t>2,2,4,3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -15233,7 +15368,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN] – Ankle Drop</t>
+          <t>Double Snake Bite – Ankle Drop</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -15310,7 +15445,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2,2 [~F],4,3,3</t>
+          <t>2,2,4,3,3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -15320,7 +15455,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Double Snake Bite [DGN] – Lift Up Cannon</t>
+          <t>Double Snake Bite – Lift Up Cannon</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -15402,22 +15537,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2,2,2 [~F]</t>
+          <t>2,2,2</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2,2,2 [~F]</t>
+          <t>2,2,2</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Triple Snake Bite [PAN]</t>
+          <t>Triple Snake Bite</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Triple Snake Bite [PAN]</t>
+          <t>Triple Snake Bite</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>(~F)PAN</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -16383,27 +16523,27 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>b+4 [d]</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>b+4 [d]</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND]</t>
+          <t>Tornado Kick</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Tornado Kick [KND]</t>
+          <t>Tornado Kick</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -16445,27 +16585,27 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>b+4,U [d]</t>
+          <t>b+4,U</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>b+4,U [d]</t>
+          <t>b+4,U</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Triple Tornado [KND]</t>
+          <t>Triple Tornado</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Triple Tornado [KND]</t>
+          <t>Triple Tornado</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>BT; (~D)KND</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">

--- a/sources/lei_step8.xlsx
+++ b/sources/lei_step8.xlsx
@@ -1000,6 +1000,11 @@
           <t>Lei regains 10 points of energy but the throw damage is reduced to 23.</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>915f6ce4-1f16-4f29-88a0-289bf4714220</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>915f6ce4-1f16-4f29-88a0-289bf4714220</t>
@@ -1067,6 +1072,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1fb94b7c-cb38-4d16-8f0b-b543560350e1</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>1fb94b7c-cb38-4d16-8f0b-b543560350e1</t>
@@ -1129,6 +1139,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>ffe412b1-5618-4c64-9fba-93d447318548</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>ffe412b1-5618-4c64-9fba-93d447318548</t>
@@ -1189,6 +1204,11 @@
       <c r="U11" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3376e300-d34c-4e03-990c-8cf3dac1403a</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -16280,6 +16300,11 @@
           <t>hhlMmmhmmh</t>
         </is>
       </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
+        </is>
+      </c>
       <c r="Z193" t="inlineStr">
         <is>
           <t>3b08195b-3ba2-4ba2-b20d-f82f3f97efcc</t>
@@ -16317,6 +16342,11 @@
           <t>hhlMmmhmLh</t>
         </is>
       </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
+        </is>
+      </c>
       <c r="Z194" t="inlineStr">
         <is>
           <t>ad8ba5a0-00eb-4959-9a6d-1b52886c113e</t>
@@ -16357,6 +16387,11 @@
       <c r="X195" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>1e9286e9-8453-4085-abd5-d467b2a34a10</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
